--- a/docs/generated/Прайс-лист.xlsx
+++ b/docs/generated/Прайс-лист.xlsx
@@ -930,10 +930,10 @@
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1200</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4800</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="17">
